--- a/real_estate_forms/012_estate_plan_client_questionnaire_template--real_estate_forms.xlsx
+++ b/real_estate_forms/012_estate_plan_client_questionnaire_template--real_estate_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,18 +510,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Enter First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Enter Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,13 +561,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Enter Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Enter Phone Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Spouse's First Name</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,13 +630,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Spouse's Last Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Spouse's Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Spouse's Phone Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_child_name</t>
+          <t>first_child</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>first_child</t>
+          <t>First Child's Name</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>First Child's Age</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>last_child_name</t>
+          <t>last_child</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>last_child</t>
+          <t>Last Child's Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>children_count</t>
+          <t>Number of Children</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dependent_first_name</t>
+          <t>Dependent's First Name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dependent_last_name</t>
+          <t>Dependent's Last Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dependent_age</t>
+          <t>Dependent's Age</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dependent_phone</t>
+          <t>Dependent's Phone Number</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dependent_email</t>
+          <t>Dependent's Email</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,85 +901,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other_dependent_first_name</t>
+          <t>other_dependents</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>Additional Dependents</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other_dependent_last_name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>other_dependent_phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other_dependent_email</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
